--- a/results/chronological/consolidated/VaR_Backtesting.xlsx
+++ b/results/chronological/consolidated/VaR_Backtesting.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -69,13 +69,31 @@
     <t xml:space="preserve">GBPUSD</t>
   </si>
   <si>
+    <t xml:space="preserve">GBPCNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">USDZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBPZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURZAR</t>
   </si>
   <si>
     <t xml:space="preserve">NVDA</t>
   </si>
   <si>
     <t xml:space="preserve">MSFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMT</t>
   </si>
   <si>
     <t xml:space="preserve">AMZN</t>
@@ -678,10 +696,10 @@
         <v>0.95</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0150146688563622</v>
+        <v>-0.00860127870257976</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0196577871163292</v>
+        <v>-0.0121924863007988</v>
       </c>
       <c r="F6" t="n">
         <v>80</v>
@@ -708,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.000738587034106786</v>
+        <v>-3.53315674889939</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -725,10 +743,10 @@
         <v>0.99</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0227928020226114</v>
+        <v>-0.0143248346854156</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0266621186222709</v>
+        <v>-0.0184925557173553</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -772,10 +790,10 @@
         <v>0.95</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0525814067934265</v>
+        <v>-0.0150146688563622</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0754043096912388</v>
+        <v>-0.0196577871163292</v>
       </c>
       <c r="F8" t="n">
         <v>80</v>
@@ -802,7 +820,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.04441805348648</v>
+        <v>-0.000738587034106786</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -819,10 +837,10 @@
         <v>0.99</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0820739931626555</v>
+        <v>-0.0227928020226114</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.115992143124377</v>
+        <v>-0.0266621186222709</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
@@ -849,7 +867,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>-6.82295794977887</v>
+        <v>-2.05479571547011</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -866,10 +884,10 @@
         <v>0.95</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.030018046052394</v>
+        <v>-0.0138914068488272</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0433314031886787</v>
+        <v>-0.0178454572159039</v>
       </c>
       <c r="F10" t="n">
         <v>80</v>
@@ -896,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.09449567488804</v>
+        <v>-0.000738587034106786</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
@@ -913,10 +931,10 @@
         <v>0.99</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0466888314021974</v>
+        <v>-0.0204316349296731</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0681733955820991</v>
+        <v>-0.0244059985239135</v>
       </c>
       <c r="F11" t="n">
         <v>16</v>
@@ -960,10 +978,10 @@
         <v>0.95</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0343868077922034</v>
+        <v>-0.0128951328873264</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0520885669761088</v>
+        <v>-0.0167381375953736</v>
       </c>
       <c r="F12" t="n">
         <v>80</v>
@@ -990,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>-11.9357650167846</v>
+        <v>-0.000738587034106786</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -1007,10 +1025,10 @@
         <v>0.99</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0609893262255769</v>
+        <v>-0.0194035138833033</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0796933139464944</v>
+        <v>-0.0230499278479395</v>
       </c>
       <c r="F13" t="n">
         <v>16</v>
@@ -1045,19 +1063,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
         <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.00754861233167929</v>
+        <v>-0.0525814067934265</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0105209176347553</v>
+        <v>-0.0754043096912388</v>
       </c>
       <c r="F14" t="n">
         <v>80</v>
@@ -1084,7 +1102,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.919537512706029</v>
+        <v>-1.04441805348648</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -1092,19 +1110,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
         <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>0.99</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0124026305340209</v>
+        <v>-0.0820739931626555</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0148602611677199</v>
+        <v>-0.115992143124377</v>
       </c>
       <c r="F15" t="n">
         <v>16</v>
@@ -1127,29 +1145,31 @@
       <c r="L15" t="b">
         <v>0</v>
       </c>
-      <c r="M15" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="N15" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="O15"/>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-6.82295794977887</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
         <v>0.95</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.00911944784032187</v>
+        <v>-0.030018046052394</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0132812972068286</v>
+        <v>-0.0433314031886787</v>
       </c>
       <c r="F16" t="n">
         <v>80</v>
@@ -1176,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.15776445500614</v>
+        <v>-2.09449567488804</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -1184,19 +1204,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
         <v>0.99</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0155851122796263</v>
+        <v>-0.0466888314021974</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0201299838969888</v>
+        <v>-0.0681733955820991</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
@@ -1223,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.9248645315104</v>
+        <v>-2.05479571547011</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -1231,19 +1251,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
         <v>0.95</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0150146688563622</v>
+        <v>-0.0182203536152379</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0196577871163292</v>
+        <v>-0.0314292485687419</v>
       </c>
       <c r="F18" t="n">
         <v>80</v>
@@ -1270,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.000738587034106786</v>
+        <v>-3.41938137955719</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -1278,19 +1298,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
         <v>0.99</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0227928020226114</v>
+        <v>-0.0387831522775009</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0266621186222709</v>
+        <v>-0.0560462586194153</v>
       </c>
       <c r="F19" t="n">
         <v>16</v>
@@ -1317,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.05479571547011</v>
+        <v>-12.9248645315104</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -1325,19 +1345,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C20" t="n">
         <v>0.95</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0525814067934265</v>
+        <v>-0.0324383672669297</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0754043096912388</v>
+        <v>-0.049555432229209</v>
       </c>
       <c r="F20" t="n">
         <v>80</v>
@@ -1364,7 +1384,7 @@
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.04441805348648</v>
+        <v>-5.14836231034565</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -1372,19 +1392,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
         <v>0.99</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0820739931626555</v>
+        <v>-0.0608143953956439</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.115992143124377</v>
+        <v>-0.0799724909308915</v>
       </c>
       <c r="F21" t="n">
         <v>16</v>
@@ -1407,31 +1427,29 @@
       <c r="L21" t="b">
         <v>0</v>
       </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-6.82295794977887</v>
-      </c>
-      <c r="O21" t="b">
-        <v>0</v>
-      </c>
+      <c r="M21" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="N21" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="O21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C22" t="n">
         <v>0.95</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.030018046052394</v>
+        <v>-0.0192426932700829</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0433314031886787</v>
+        <v>-0.0321081968278416</v>
       </c>
       <c r="F22" t="n">
         <v>80</v>
@@ -1458,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.09449567488804</v>
+        <v>-3.41938137955719</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -1466,19 +1484,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C23" t="n">
         <v>0.99</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0466888314021974</v>
+        <v>-0.0353401499116603</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0681733955820991</v>
+        <v>-0.0652567331747006</v>
       </c>
       <c r="F23" t="n">
         <v>16</v>
@@ -1505,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.05479571547011</v>
+        <v>-6.82295794977887</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -1513,10 +1531,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C24" t="n">
         <v>0.95</v>
@@ -1560,10 +1578,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C25" t="n">
         <v>0.99</v>
@@ -1607,7 +1625,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
@@ -1654,7 +1672,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
@@ -1699,7 +1717,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -1746,7 +1764,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -1793,7 +1811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
         <v>18</v>
@@ -1802,10 +1820,10 @@
         <v>0.95</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0150146688563622</v>
+        <v>-0.00860127870257976</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0196577871163292</v>
+        <v>-0.0121924863007988</v>
       </c>
       <c r="F30" t="n">
         <v>80</v>
@@ -1832,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.000738587034106786</v>
+        <v>-3.53315674889939</v>
       </c>
       <c r="O30" t="b">
         <v>0</v>
@@ -1840,7 +1858,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
         <v>18</v>
@@ -1849,10 +1867,10 @@
         <v>0.99</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0227928020226114</v>
+        <v>-0.0143248346854156</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0266621186222709</v>
+        <v>-0.0184925557173553</v>
       </c>
       <c r="F31" t="n">
         <v>16</v>
@@ -1887,7 +1905,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
         <v>19</v>
@@ -1896,10 +1914,10 @@
         <v>0.95</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0525814067934265</v>
+        <v>-0.0150146688563622</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0754043096912388</v>
+        <v>-0.0196577871163292</v>
       </c>
       <c r="F32" t="n">
         <v>80</v>
@@ -1926,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.04441805348648</v>
+        <v>-0.000738587034106786</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
@@ -1934,7 +1952,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
@@ -1943,10 +1961,10 @@
         <v>0.99</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0820739931626555</v>
+        <v>-0.0227928020226114</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.115992143124377</v>
+        <v>-0.0266621186222709</v>
       </c>
       <c r="F33" t="n">
         <v>16</v>
@@ -1973,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>-6.82295794977887</v>
+        <v>-2.05479571547011</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
@@ -1981,7 +1999,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
         <v>20</v>
@@ -1990,10 +2008,10 @@
         <v>0.95</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.030018046052394</v>
+        <v>-0.0138914068488272</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0433314031886787</v>
+        <v>-0.0178454572159039</v>
       </c>
       <c r="F34" t="n">
         <v>80</v>
@@ -2020,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>-2.09449567488804</v>
+        <v>-0.000738587034106786</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
@@ -2028,7 +2046,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
         <v>20</v>
@@ -2037,10 +2055,10 @@
         <v>0.99</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0466888314021974</v>
+        <v>-0.0204316349296731</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0681733955820991</v>
+        <v>-0.0244059985239135</v>
       </c>
       <c r="F35" t="n">
         <v>16</v>
@@ -2075,7 +2093,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
@@ -2084,10 +2102,10 @@
         <v>0.95</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0343868077922034</v>
+        <v>-0.0128951328873264</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0520885669761088</v>
+        <v>-0.0167381375953736</v>
       </c>
       <c r="F36" t="n">
         <v>80</v>
@@ -2114,7 +2132,7 @@
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>-11.9357650167846</v>
+        <v>-0.000738587034106786</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
@@ -2122,7 +2140,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B37" t="s">
         <v>21</v>
@@ -2131,10 +2149,10 @@
         <v>0.99</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0609893262255769</v>
+        <v>-0.0194035138833033</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.0796933139464944</v>
+        <v>-0.0230499278479395</v>
       </c>
       <c r="F37" t="n">
         <v>16</v>
@@ -2169,19 +2187,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C38" t="n">
         <v>0.95</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.00754861233167929</v>
+        <v>-0.0525814067934265</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.0105209176347553</v>
+        <v>-0.0754043096912388</v>
       </c>
       <c r="F38" t="n">
         <v>80</v>
@@ -2208,7 +2226,7 @@
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.919537512706029</v>
+        <v>-1.04441805348648</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
@@ -2216,19 +2234,19 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C39" t="n">
         <v>0.99</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0124026305340209</v>
+        <v>-0.0820739931626555</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0148602611677199</v>
+        <v>-0.115992143124377</v>
       </c>
       <c r="F39" t="n">
         <v>16</v>
@@ -2251,29 +2269,31 @@
       <c r="L39" t="b">
         <v>0</v>
       </c>
-      <c r="M39" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="N39" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="O39"/>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-6.82295794977887</v>
+      </c>
+      <c r="O39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C40" t="n">
         <v>0.95</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.00911944784032187</v>
+        <v>-0.030018046052394</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.0132812972068286</v>
+        <v>-0.0433314031886787</v>
       </c>
       <c r="F40" t="n">
         <v>80</v>
@@ -2300,7 +2320,7 @@
         <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>-7.15776445500614</v>
+        <v>-2.09449567488804</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
@@ -2308,19 +2328,19 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C41" t="n">
         <v>0.99</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0155851122796263</v>
+        <v>-0.0466888314021974</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0201299838969888</v>
+        <v>-0.0681733955820991</v>
       </c>
       <c r="F41" t="n">
         <v>16</v>
@@ -2347,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>-12.9248645315104</v>
+        <v>-2.05479571547011</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
@@ -2355,19 +2375,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
         <v>24</v>
-      </c>
-      <c r="B42" t="s">
-        <v>18</v>
       </c>
       <c r="C42" t="n">
         <v>0.95</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0150146688563622</v>
+        <v>-0.0182203536152379</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.0196577871163292</v>
+        <v>-0.0314292485687419</v>
       </c>
       <c r="F42" t="n">
         <v>80</v>
@@ -2394,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.000738587034106786</v>
+        <v>-3.41938137955719</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
@@ -2402,19 +2422,19 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
         <v>24</v>
-      </c>
-      <c r="B43" t="s">
-        <v>18</v>
       </c>
       <c r="C43" t="n">
         <v>0.99</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0227928020226114</v>
+        <v>-0.0387831522775009</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.0266621186222709</v>
+        <v>-0.0560462586194153</v>
       </c>
       <c r="F43" t="n">
         <v>16</v>
@@ -2441,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>-2.05479571547011</v>
+        <v>-12.9248645315104</v>
       </c>
       <c r="O43" t="b">
         <v>0</v>
@@ -2449,19 +2469,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C44" t="n">
         <v>0.95</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0525814067934265</v>
+        <v>-0.0324383672669297</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.0754043096912388</v>
+        <v>-0.049555432229209</v>
       </c>
       <c r="F44" t="n">
         <v>80</v>
@@ -2488,7 +2508,7 @@
         <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>-1.04441805348648</v>
+        <v>-5.14836231034565</v>
       </c>
       <c r="O44" t="b">
         <v>0</v>
@@ -2496,19 +2516,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C45" t="n">
         <v>0.99</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0820739931626555</v>
+        <v>-0.0608143953956439</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.115992143124377</v>
+        <v>-0.0799724909308915</v>
       </c>
       <c r="F45" t="n">
         <v>16</v>
@@ -2531,31 +2551,29 @@
       <c r="L45" t="b">
         <v>0</v>
       </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-6.82295794977887</v>
-      </c>
-      <c r="O45" t="b">
-        <v>0</v>
-      </c>
+      <c r="M45" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="N45" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="O45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C46" t="n">
         <v>0.95</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.030018046052394</v>
+        <v>-0.0192426932700829</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0433314031886787</v>
+        <v>-0.0321081968278416</v>
       </c>
       <c r="F46" t="n">
         <v>80</v>
@@ -2582,7 +2600,7 @@
         <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>-2.09449567488804</v>
+        <v>-3.41938137955719</v>
       </c>
       <c r="O46" t="b">
         <v>0</v>
@@ -2590,19 +2608,19 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C47" t="n">
         <v>0.99</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0466888314021974</v>
+        <v>-0.0353401499116603</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0681733955820991</v>
+        <v>-0.0652567331747006</v>
       </c>
       <c r="F47" t="n">
         <v>16</v>
@@ -2629,7 +2647,7 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>-2.05479571547011</v>
+        <v>-6.82295794977887</v>
       </c>
       <c r="O47" t="b">
         <v>0</v>
@@ -2637,10 +2655,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C48" t="n">
         <v>0.95</v>
@@ -2684,10 +2702,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C49" t="n">
         <v>0.99</v>
@@ -2726,6 +2744,2254 @@
         <v>-2.05479571547011</v>
       </c>
       <c r="O49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.00754861233167929</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-0.0105209176347553</v>
+      </c>
+      <c r="F50" t="n">
+        <v>80</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-0.919537512706029</v>
+      </c>
+      <c r="O50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-0.0124026305340209</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.0148602611677199</v>
+      </c>
+      <c r="F51" t="n">
+        <v>16</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="N51" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="O51"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.00911944784032187</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.0132812972068286</v>
+      </c>
+      <c r="F52" t="n">
+        <v>80</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-7.15776445500614</v>
+      </c>
+      <c r="O52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-0.0155851122796263</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.0201299838969888</v>
+      </c>
+      <c r="F53" t="n">
+        <v>16</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-12.9248645315104</v>
+      </c>
+      <c r="O53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-0.00860127870257976</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.0121924863007988</v>
+      </c>
+      <c r="F54" t="n">
+        <v>80</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-3.53315674889939</v>
+      </c>
+      <c r="O54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>29</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.0143248346854156</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.0184925557173553</v>
+      </c>
+      <c r="F55" t="n">
+        <v>16</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.0150146688563622</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.0196577871163292</v>
+      </c>
+      <c r="F56" t="n">
+        <v>80</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-0.000738587034106786</v>
+      </c>
+      <c r="O56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.0227928020226114</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.0266621186222709</v>
+      </c>
+      <c r="F57" t="n">
+        <v>16</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>29</v>
+      </c>
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.0138914068488272</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.0178454572159039</v>
+      </c>
+      <c r="F58" t="n">
+        <v>80</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-0.000738587034106786</v>
+      </c>
+      <c r="O58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.0204316349296731</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-0.0244059985239135</v>
+      </c>
+      <c r="F59" t="n">
+        <v>16</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>29</v>
+      </c>
+      <c r="B60" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.0128951328873264</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.0167381375953736</v>
+      </c>
+      <c r="F60" t="n">
+        <v>80</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-0.000738587034106786</v>
+      </c>
+      <c r="O60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>29</v>
+      </c>
+      <c r="B61" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-0.0194035138833033</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.0230499278479395</v>
+      </c>
+      <c r="F61" t="n">
+        <v>16</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>29</v>
+      </c>
+      <c r="B62" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-0.0525814067934265</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.0754043096912388</v>
+      </c>
+      <c r="F62" t="n">
+        <v>80</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-1.04441805348648</v>
+      </c>
+      <c r="O62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>29</v>
+      </c>
+      <c r="B63" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-0.0820739931626555</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.115992143124377</v>
+      </c>
+      <c r="F63" t="n">
+        <v>16</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-6.82295794977887</v>
+      </c>
+      <c r="O63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>29</v>
+      </c>
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-0.030018046052394</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.0433314031886787</v>
+      </c>
+      <c r="F64" t="n">
+        <v>80</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-2.09449567488804</v>
+      </c>
+      <c r="O64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>29</v>
+      </c>
+      <c r="B65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-0.0466888314021974</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-0.0681733955820991</v>
+      </c>
+      <c r="F65" t="n">
+        <v>16</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-0.0182203536152379</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-0.0314292485687419</v>
+      </c>
+      <c r="F66" t="n">
+        <v>80</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-3.41938137955719</v>
+      </c>
+      <c r="O66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>29</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-0.0387831522775009</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-0.0560462586194153</v>
+      </c>
+      <c r="F67" t="n">
+        <v>16</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-12.9248645315104</v>
+      </c>
+      <c r="O67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>29</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-0.0324383672669297</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-0.049555432229209</v>
+      </c>
+      <c r="F68" t="n">
+        <v>80</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-5.14836231034565</v>
+      </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>29</v>
+      </c>
+      <c r="B69" t="s">
+        <v>25</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-0.0608143953956439</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-0.0799724909308915</v>
+      </c>
+      <c r="F69" t="n">
+        <v>16</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="N69" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="O69"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>29</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-0.0192426932700829</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.0321081968278416</v>
+      </c>
+      <c r="F70" t="n">
+        <v>80</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-3.41938137955719</v>
+      </c>
+      <c r="O70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>29</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-0.0353401499116603</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-0.0652567331747006</v>
+      </c>
+      <c r="F71" t="n">
+        <v>16</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-6.82295794977887</v>
+      </c>
+      <c r="O71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>29</v>
+      </c>
+      <c r="B72" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-0.0343868077922034</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-0.0520885669761088</v>
+      </c>
+      <c r="F72" t="n">
+        <v>80</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-11.9357650167846</v>
+      </c>
+      <c r="O72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>29</v>
+      </c>
+      <c r="B73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-0.0609893262255769</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-0.0796933139464944</v>
+      </c>
+      <c r="F73" t="n">
+        <v>16</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>30</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-0.00754861233167929</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-0.0105209176347553</v>
+      </c>
+      <c r="F74" t="n">
+        <v>80</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-0.919537512706029</v>
+      </c>
+      <c r="O74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-0.0124026305340209</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-0.0148602611677199</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="N75" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="O75"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>30</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-0.00911944784032187</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-0.0132812972068286</v>
+      </c>
+      <c r="F76" t="n">
+        <v>80</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L76" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-7.15776445500614</v>
+      </c>
+      <c r="O76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-0.0155851122796263</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-0.0201299838969888</v>
+      </c>
+      <c r="F77" t="n">
+        <v>16</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" t="n">
+        <v>-12.9248645315104</v>
+      </c>
+      <c r="O77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-0.00860127870257976</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-0.0121924863007988</v>
+      </c>
+      <c r="F78" t="n">
+        <v>80</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L78" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-3.53315674889939</v>
+      </c>
+      <c r="O78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-0.0143248346854156</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-0.0184925557173553</v>
+      </c>
+      <c r="F79" t="n">
+        <v>16</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-0.0150146688563622</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-0.0196577871163292</v>
+      </c>
+      <c r="F80" t="n">
+        <v>80</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L80" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-0.000738587034106786</v>
+      </c>
+      <c r="O80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-0.0227928020226114</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-0.0266621186222709</v>
+      </c>
+      <c r="F81" t="n">
+        <v>16</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L81" t="b">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-0.0138914068488272</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-0.0178454572159039</v>
+      </c>
+      <c r="F82" t="n">
+        <v>80</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L82" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-0.000738587034106786</v>
+      </c>
+      <c r="O82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-0.0204316349296731</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-0.0244059985239135</v>
+      </c>
+      <c r="F83" t="n">
+        <v>16</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L83" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>30</v>
+      </c>
+      <c r="B84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-0.0128951328873264</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-0.0167381375953736</v>
+      </c>
+      <c r="F84" t="n">
+        <v>80</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L84" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-0.000738587034106786</v>
+      </c>
+      <c r="O84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-0.0194035138833033</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-0.0230499278479395</v>
+      </c>
+      <c r="F85" t="n">
+        <v>16</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L85" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>30</v>
+      </c>
+      <c r="B86" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-0.0525814067934265</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-0.0754043096912388</v>
+      </c>
+      <c r="F86" t="n">
+        <v>80</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L86" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-1.04441805348648</v>
+      </c>
+      <c r="O86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>30</v>
+      </c>
+      <c r="B87" t="s">
+        <v>22</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-0.0820739931626555</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-0.115992143124377</v>
+      </c>
+      <c r="F87" t="n">
+        <v>16</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L87" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-6.82295794977887</v>
+      </c>
+      <c r="O87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-0.030018046052394</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-0.0433314031886787</v>
+      </c>
+      <c r="F88" t="n">
+        <v>80</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L88" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-2.09449567488804</v>
+      </c>
+      <c r="O88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>30</v>
+      </c>
+      <c r="B89" t="s">
+        <v>23</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-0.0466888314021974</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-0.0681733955820991</v>
+      </c>
+      <c r="F89" t="n">
+        <v>16</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L89" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>30</v>
+      </c>
+      <c r="B90" t="s">
+        <v>24</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-0.0182203536152379</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-0.0314292485687419</v>
+      </c>
+      <c r="F90" t="n">
+        <v>80</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L90" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>-3.41938137955719</v>
+      </c>
+      <c r="O90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-0.0387831522775009</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-0.0560462586194153</v>
+      </c>
+      <c r="F91" t="n">
+        <v>16</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L91" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-12.9248645315104</v>
+      </c>
+      <c r="O91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" t="s">
+        <v>25</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-0.0324383672669297</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-0.049555432229209</v>
+      </c>
+      <c r="F92" t="n">
+        <v>80</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L92" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" t="n">
+        <v>-5.14836231034565</v>
+      </c>
+      <c r="O92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>30</v>
+      </c>
+      <c r="B93" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-0.0608143953956439</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-0.0799724909308915</v>
+      </c>
+      <c r="F93" t="n">
+        <v>16</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L93" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="N93" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="O93"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-0.0192426932700829</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-0.0321081968278416</v>
+      </c>
+      <c r="F94" t="n">
+        <v>80</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L94" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" t="n">
+        <v>-3.41938137955719</v>
+      </c>
+      <c r="O94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>30</v>
+      </c>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-0.0353401499116603</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-0.0652567331747006</v>
+      </c>
+      <c r="F95" t="n">
+        <v>16</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L95" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-6.82295794977887</v>
+      </c>
+      <c r="O95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" t="s">
+        <v>27</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-0.0343868077922034</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-0.0520885669761088</v>
+      </c>
+      <c r="F96" t="n">
+        <v>80</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.0506008855154965</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-0.0119723751888046</v>
+      </c>
+      <c r="L96" t="b">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-11.9357650167846</v>
+      </c>
+      <c r="O96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>30</v>
+      </c>
+      <c r="B97" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-0.0609893262255769</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-0.0796933139464944</v>
+      </c>
+      <c r="F97" t="n">
+        <v>16</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1581</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.0101201771030993</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-0.00229733781463892</v>
+      </c>
+      <c r="L97" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-2.05479571547011</v>
+      </c>
+      <c r="O97" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2748,27 +5014,27 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B2" t="n">
         <v>0.95</v>
@@ -2794,7 +5060,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B3" t="n">
         <v>0.99</v>
@@ -2820,7 +5086,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B4" t="n">
         <v>0.95</v>
@@ -2846,7 +5112,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B5" t="n">
         <v>0.99</v>
@@ -2872,7 +5138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B6" t="n">
         <v>0.95</v>
@@ -2898,7 +5164,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B7" t="n">
         <v>0.99</v>

--- a/results/chronological/consolidated/VaR_Backtesting.xlsx
+++ b/results/chronological/consolidated/VaR_Backtesting.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -69,31 +69,13 @@
     <t xml:space="preserve">GBPUSD</t>
   </si>
   <si>
-    <t xml:space="preserve">GBPCNY</t>
-  </si>
-  <si>
     <t xml:space="preserve">USDZAR</t>
   </si>
   <si>
-    <t xml:space="preserve">GBPZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EURZAR</t>
-  </si>
-  <si>
     <t xml:space="preserve">NVDA</t>
   </si>
   <si>
     <t xml:space="preserve">MSFT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WMT</t>
   </si>
   <si>
     <t xml:space="preserve">AMZN</t>
@@ -696,10 +678,10 @@
         <v>0.95</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00860127870257976</v>
+        <v>-0.0150146688563622</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0121924863007988</v>
+        <v>-0.0196577871163292</v>
       </c>
       <c r="F6" t="n">
         <v>80</v>
@@ -726,7 +708,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.53315674889939</v>
+        <v>-0.000738587034106786</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
@@ -743,10 +725,10 @@
         <v>0.99</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0143248346854156</v>
+        <v>-0.0227928020226114</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0184925557173553</v>
+        <v>-0.0266621186222709</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -790,10 +772,10 @@
         <v>0.95</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0150146688563622</v>
+        <v>-0.0525814067934265</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0196577871163292</v>
+        <v>-0.0754043096912388</v>
       </c>
       <c r="F8" t="n">
         <v>80</v>
@@ -820,7 +802,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.000738587034106786</v>
+        <v>-1.04441805348648</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -837,10 +819,10 @@
         <v>0.99</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0227928020226114</v>
+        <v>-0.0820739931626555</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0266621186222709</v>
+        <v>-0.115992143124377</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
@@ -867,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.05479571547011</v>
+        <v>-6.82295794977887</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
@@ -884,10 +866,10 @@
         <v>0.95</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0138914068488272</v>
+        <v>-0.030018046052394</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0178454572159039</v>
+        <v>-0.0433314031886787</v>
       </c>
       <c r="F10" t="n">
         <v>80</v>
@@ -914,7 +896,7 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.000738587034106786</v>
+        <v>-2.09449567488804</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
@@ -931,10 +913,10 @@
         <v>0.99</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0204316349296731</v>
+        <v>-0.0466888314021974</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0244059985239135</v>
+        <v>-0.0681733955820991</v>
       </c>
       <c r="F11" t="n">
         <v>16</v>
@@ -978,10 +960,10 @@
         <v>0.95</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0128951328873264</v>
+        <v>-0.0343868077922034</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0167381375953736</v>
+        <v>-0.0520885669761088</v>
       </c>
       <c r="F12" t="n">
         <v>80</v>
@@ -1008,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.000738587034106786</v>
+        <v>-11.9357650167846</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -1025,10 +1007,10 @@
         <v>0.99</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0194035138833033</v>
+        <v>-0.0609893262255769</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0230499278479395</v>
+        <v>-0.0796933139464944</v>
       </c>
       <c r="F13" t="n">
         <v>16</v>
@@ -1063,19 +1045,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0525814067934265</v>
+        <v>-0.00754861233167929</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0754043096912388</v>
+        <v>-0.0105209176347553</v>
       </c>
       <c r="F14" t="n">
         <v>80</v>
@@ -1102,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.04441805348648</v>
+        <v>-0.919537512706029</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -1110,19 +1092,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>0.99</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0820739931626555</v>
+        <v>-0.0124026305340209</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.115992143124377</v>
+        <v>-0.0148602611677199</v>
       </c>
       <c r="F15" t="n">
         <v>16</v>
@@ -1145,31 +1127,29 @@
       <c r="L15" t="b">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-6.82295794977887</v>
-      </c>
-      <c r="O15" t="b">
-        <v>0</v>
-      </c>
+      <c r="M15" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="N15" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="O15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>0.95</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.030018046052394</v>
+        <v>-0.00911944784032187</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0433314031886787</v>
+        <v>-0.0132812972068286</v>
       </c>
       <c r="F16" t="n">
         <v>80</v>
@@ -1196,7 +1176,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.09449567488804</v>
+        <v>-7.15776445500614</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -1204,19 +1184,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>0.99</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0466888314021974</v>
+        <v>-0.0155851122796263</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0681733955820991</v>
+        <v>-0.0201299838969888</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
@@ -1243,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.05479571547011</v>
+        <v>-12.9248645315104</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -1251,19 +1231,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
         <v>0.95</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0182203536152379</v>
+        <v>-0.0150146688563622</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0314292485687419</v>
+        <v>-0.0196577871163292</v>
       </c>
       <c r="F18" t="n">
         <v>80</v>
@@ -1290,7 +1270,7 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.41938137955719</v>
+        <v>-0.000738587034106786</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -1298,19 +1278,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
         <v>0.99</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0387831522775009</v>
+        <v>-0.0227928020226114</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0560462586194153</v>
+        <v>-0.0266621186222709</v>
       </c>
       <c r="F19" t="n">
         <v>16</v>
@@ -1337,7 +1317,7 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>-12.9248645315104</v>
+        <v>-2.05479571547011</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -1345,19 +1325,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
         <v>0.95</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0324383672669297</v>
+        <v>-0.0525814067934265</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.049555432229209</v>
+        <v>-0.0754043096912388</v>
       </c>
       <c r="F20" t="n">
         <v>80</v>
@@ -1384,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>-5.14836231034565</v>
+        <v>-1.04441805348648</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -1392,19 +1372,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
         <v>0.99</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0608143953956439</v>
+        <v>-0.0820739931626555</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0799724909308915</v>
+        <v>-0.115992143124377</v>
       </c>
       <c r="F21" t="n">
         <v>16</v>
@@ -1427,29 +1407,31 @@
       <c r="L21" t="b">
         <v>0</v>
       </c>
-      <c r="M21" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="N21" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="O21"/>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-6.82295794977887</v>
+      </c>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
         <v>0.95</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0192426932700829</v>
+        <v>-0.030018046052394</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0321081968278416</v>
+        <v>-0.0433314031886787</v>
       </c>
       <c r="F22" t="n">
         <v>80</v>
@@ -1476,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.41938137955719</v>
+        <v>-2.09449567488804</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -1484,19 +1466,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C23" t="n">
         <v>0.99</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0353401499116603</v>
+        <v>-0.0466888314021974</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0652567331747006</v>
+        <v>-0.0681733955820991</v>
       </c>
       <c r="F23" t="n">
         <v>16</v>
@@ -1523,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>-6.82295794977887</v>
+        <v>-2.05479571547011</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -1531,10 +1513,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C24" t="n">
         <v>0.95</v>
@@ -1578,10 +1560,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C25" t="n">
         <v>0.99</v>
@@ -1625,7 +1607,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
@@ -1672,7 +1654,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
@@ -1717,7 +1699,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -1764,7 +1746,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -1811,7 +1793,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
         <v>18</v>
@@ -1820,10 +1802,10 @@
         <v>0.95</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.00860127870257976</v>
+        <v>-0.0150146688563622</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0121924863007988</v>
+        <v>-0.0196577871163292</v>
       </c>
       <c r="F30" t="n">
         <v>80</v>
@@ -1850,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>-3.53315674889939</v>
+        <v>-0.000738587034106786</v>
       </c>
       <c r="O30" t="b">
         <v>0</v>
@@ -1858,7 +1840,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
         <v>18</v>
@@ -1867,10 +1849,10 @@
         <v>0.99</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0143248346854156</v>
+        <v>-0.0227928020226114</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0184925557173553</v>
+        <v>-0.0266621186222709</v>
       </c>
       <c r="F31" t="n">
         <v>16</v>
@@ -1905,7 +1887,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
         <v>19</v>
@@ -1914,10 +1896,10 @@
         <v>0.95</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0150146688563622</v>
+        <v>-0.0525814067934265</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0196577871163292</v>
+        <v>-0.0754043096912388</v>
       </c>
       <c r="F32" t="n">
         <v>80</v>
@@ -1944,7 +1926,7 @@
         <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.000738587034106786</v>
+        <v>-1.04441805348648</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
@@ -1952,7 +1934,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
@@ -1961,10 +1943,10 @@
         <v>0.99</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0227928020226114</v>
+        <v>-0.0820739931626555</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0266621186222709</v>
+        <v>-0.115992143124377</v>
       </c>
       <c r="F33" t="n">
         <v>16</v>
@@ -1991,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>-2.05479571547011</v>
+        <v>-6.82295794977887</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
@@ -1999,7 +1981,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
         <v>20</v>
@@ -2008,10 +1990,10 @@
         <v>0.95</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0138914068488272</v>
+        <v>-0.030018046052394</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0178454572159039</v>
+        <v>-0.0433314031886787</v>
       </c>
       <c r="F34" t="n">
         <v>80</v>
@@ -2038,7 +2020,7 @@
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.000738587034106786</v>
+        <v>-2.09449567488804</v>
       </c>
       <c r="O34" t="b">
         <v>0</v>
@@ -2046,7 +2028,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
         <v>20</v>
@@ -2055,10 +2037,10 @@
         <v>0.99</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0204316349296731</v>
+        <v>-0.0466888314021974</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0244059985239135</v>
+        <v>-0.0681733955820991</v>
       </c>
       <c r="F35" t="n">
         <v>16</v>
@@ -2093,7 +2075,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
@@ -2102,10 +2084,10 @@
         <v>0.95</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0128951328873264</v>
+        <v>-0.0343868077922034</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0167381375953736</v>
+        <v>-0.0520885669761088</v>
       </c>
       <c r="F36" t="n">
         <v>80</v>
@@ -2132,7 +2114,7 @@
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.000738587034106786</v>
+        <v>-11.9357650167846</v>
       </c>
       <c r="O36" t="b">
         <v>0</v>
@@ -2140,7 +2122,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
         <v>21</v>
@@ -2149,10 +2131,10 @@
         <v>0.99</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0194035138833033</v>
+        <v>-0.0609893262255769</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.0230499278479395</v>
+        <v>-0.0796933139464944</v>
       </c>
       <c r="F37" t="n">
         <v>16</v>
@@ -2187,19 +2169,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C38" t="n">
         <v>0.95</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0525814067934265</v>
+        <v>-0.00754861233167929</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.0754043096912388</v>
+        <v>-0.0105209176347553</v>
       </c>
       <c r="F38" t="n">
         <v>80</v>
@@ -2226,7 +2208,7 @@
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>-1.04441805348648</v>
+        <v>-0.919537512706029</v>
       </c>
       <c r="O38" t="b">
         <v>0</v>
@@ -2234,19 +2216,19 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C39" t="n">
         <v>0.99</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0820739931626555</v>
+        <v>-0.0124026305340209</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.115992143124377</v>
+        <v>-0.0148602611677199</v>
       </c>
       <c r="F39" t="n">
         <v>16</v>
@@ -2269,31 +2251,29 @@
       <c r="L39" t="b">
         <v>0</v>
       </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-6.82295794977887</v>
-      </c>
-      <c r="O39" t="b">
-        <v>0</v>
-      </c>
+      <c r="M39" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="N39" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="O39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C40" t="n">
         <v>0.95</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.030018046052394</v>
+        <v>-0.00911944784032187</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.0433314031886787</v>
+        <v>-0.0132812972068286</v>
       </c>
       <c r="F40" t="n">
         <v>80</v>
@@ -2320,7 +2300,7 @@
         <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>-2.09449567488804</v>
+        <v>-7.15776445500614</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
@@ -2328,19 +2308,19 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C41" t="n">
         <v>0.99</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0466888314021974</v>
+        <v>-0.0155851122796263</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0681733955820991</v>
+        <v>-0.0201299838969888</v>
       </c>
       <c r="F41" t="n">
         <v>16</v>
@@ -2367,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>-2.05479571547011</v>
+        <v>-12.9248645315104</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
@@ -2375,19 +2355,19 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C42" t="n">
         <v>0.95</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0182203536152379</v>
+        <v>-0.0150146688563622</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.0314292485687419</v>
+        <v>-0.0196577871163292</v>
       </c>
       <c r="F42" t="n">
         <v>80</v>
@@ -2414,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>-3.41938137955719</v>
+        <v>-0.000738587034106786</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
@@ -2422,19 +2402,19 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C43" t="n">
         <v>0.99</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0387831522775009</v>
+        <v>-0.0227928020226114</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.0560462586194153</v>
+        <v>-0.0266621186222709</v>
       </c>
       <c r="F43" t="n">
         <v>16</v>
@@ -2461,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>-12.9248645315104</v>
+        <v>-2.05479571547011</v>
       </c>
       <c r="O43" t="b">
         <v>0</v>
@@ -2469,19 +2449,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C44" t="n">
         <v>0.95</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0324383672669297</v>
+        <v>-0.0525814067934265</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.049555432229209</v>
+        <v>-0.0754043096912388</v>
       </c>
       <c r="F44" t="n">
         <v>80</v>
@@ -2508,7 +2488,7 @@
         <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>-5.14836231034565</v>
+        <v>-1.04441805348648</v>
       </c>
       <c r="O44" t="b">
         <v>0</v>
@@ -2516,19 +2496,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C45" t="n">
         <v>0.99</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0608143953956439</v>
+        <v>-0.0820739931626555</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0799724909308915</v>
+        <v>-0.115992143124377</v>
       </c>
       <c r="F45" t="n">
         <v>16</v>
@@ -2551,29 +2531,31 @@
       <c r="L45" t="b">
         <v>0</v>
       </c>
-      <c r="M45" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="N45" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="O45"/>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-6.82295794977887</v>
+      </c>
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C46" t="n">
         <v>0.95</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0192426932700829</v>
+        <v>-0.030018046052394</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0321081968278416</v>
+        <v>-0.0433314031886787</v>
       </c>
       <c r="F46" t="n">
         <v>80</v>
@@ -2600,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>-3.41938137955719</v>
+        <v>-2.09449567488804</v>
       </c>
       <c r="O46" t="b">
         <v>0</v>
@@ -2608,19 +2590,19 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C47" t="n">
         <v>0.99</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0353401499116603</v>
+        <v>-0.0466888314021974</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0652567331747006</v>
+        <v>-0.0681733955820991</v>
       </c>
       <c r="F47" t="n">
         <v>16</v>
@@ -2647,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>-6.82295794977887</v>
+        <v>-2.05479571547011</v>
       </c>
       <c r="O47" t="b">
         <v>0</v>
@@ -2655,10 +2637,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C48" t="n">
         <v>0.95</v>
@@ -2702,10 +2684,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C49" t="n">
         <v>0.99</v>
@@ -2744,2254 +2726,6 @@
         <v>-2.05479571547011</v>
       </c>
       <c r="O49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>29</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-0.00754861233167929</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-0.0105209176347553</v>
-      </c>
-      <c r="F50" t="n">
-        <v>80</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L50" t="b">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-0.919537512706029</v>
-      </c>
-      <c r="O50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D51" t="n">
-        <v>-0.0124026305340209</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-0.0148602611677199</v>
-      </c>
-      <c r="F51" t="n">
-        <v>16</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L51" t="b">
-        <v>0</v>
-      </c>
-      <c r="M51" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="N51" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="O51"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>29</v>
-      </c>
-      <c r="B52" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D52" t="n">
-        <v>-0.00911944784032187</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-0.0132812972068286</v>
-      </c>
-      <c r="F52" t="n">
-        <v>80</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L52" t="b">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" t="n">
-        <v>-7.15776445500614</v>
-      </c>
-      <c r="O52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>29</v>
-      </c>
-      <c r="B53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-0.0155851122796263</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-0.0201299838969888</v>
-      </c>
-      <c r="F53" t="n">
-        <v>16</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L53" t="b">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-12.9248645315104</v>
-      </c>
-      <c r="O53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>29</v>
-      </c>
-      <c r="B54" t="s">
-        <v>18</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D54" t="n">
-        <v>-0.00860127870257976</v>
-      </c>
-      <c r="E54" t="n">
-        <v>-0.0121924863007988</v>
-      </c>
-      <c r="F54" t="n">
-        <v>80</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L54" t="b">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" t="n">
-        <v>-3.53315674889939</v>
-      </c>
-      <c r="O54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>29</v>
-      </c>
-      <c r="B55" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D55" t="n">
-        <v>-0.0143248346854156</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-0.0184925557173553</v>
-      </c>
-      <c r="F55" t="n">
-        <v>16</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L55" t="b">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>29</v>
-      </c>
-      <c r="B56" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-0.0150146688563622</v>
-      </c>
-      <c r="E56" t="n">
-        <v>-0.0196577871163292</v>
-      </c>
-      <c r="F56" t="n">
-        <v>80</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L56" t="b">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>-0.000738587034106786</v>
-      </c>
-      <c r="O56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>29</v>
-      </c>
-      <c r="B57" t="s">
-        <v>19</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D57" t="n">
-        <v>-0.0227928020226114</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-0.0266621186222709</v>
-      </c>
-      <c r="F57" t="n">
-        <v>16</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L57" t="b">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>29</v>
-      </c>
-      <c r="B58" t="s">
-        <v>20</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-0.0138914068488272</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-0.0178454572159039</v>
-      </c>
-      <c r="F58" t="n">
-        <v>80</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L58" t="b">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N58" t="n">
-        <v>-0.000738587034106786</v>
-      </c>
-      <c r="O58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>29</v>
-      </c>
-      <c r="B59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-0.0204316349296731</v>
-      </c>
-      <c r="E59" t="n">
-        <v>-0.0244059985239135</v>
-      </c>
-      <c r="F59" t="n">
-        <v>16</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L59" t="b">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>29</v>
-      </c>
-      <c r="B60" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-0.0128951328873264</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-0.0167381375953736</v>
-      </c>
-      <c r="F60" t="n">
-        <v>80</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L60" t="b">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-0.000738587034106786</v>
-      </c>
-      <c r="O60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>29</v>
-      </c>
-      <c r="B61" t="s">
-        <v>21</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D61" t="n">
-        <v>-0.0194035138833033</v>
-      </c>
-      <c r="E61" t="n">
-        <v>-0.0230499278479395</v>
-      </c>
-      <c r="F61" t="n">
-        <v>16</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L61" t="b">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>29</v>
-      </c>
-      <c r="B62" t="s">
-        <v>22</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D62" t="n">
-        <v>-0.0525814067934265</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-0.0754043096912388</v>
-      </c>
-      <c r="F62" t="n">
-        <v>80</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L62" t="b">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>-1.04441805348648</v>
-      </c>
-      <c r="O62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>29</v>
-      </c>
-      <c r="B63" t="s">
-        <v>22</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-0.0820739931626555</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-0.115992143124377</v>
-      </c>
-      <c r="F63" t="n">
-        <v>16</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L63" t="b">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>-6.82295794977887</v>
-      </c>
-      <c r="O63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>29</v>
-      </c>
-      <c r="B64" t="s">
-        <v>23</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-0.030018046052394</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-0.0433314031886787</v>
-      </c>
-      <c r="F64" t="n">
-        <v>80</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L64" t="b">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>1</v>
-      </c>
-      <c r="N64" t="n">
-        <v>-2.09449567488804</v>
-      </c>
-      <c r="O64" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>29</v>
-      </c>
-      <c r="B65" t="s">
-        <v>23</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-0.0466888314021974</v>
-      </c>
-      <c r="E65" t="n">
-        <v>-0.0681733955820991</v>
-      </c>
-      <c r="F65" t="n">
-        <v>16</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L65" t="b">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>29</v>
-      </c>
-      <c r="B66" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D66" t="n">
-        <v>-0.0182203536152379</v>
-      </c>
-      <c r="E66" t="n">
-        <v>-0.0314292485687419</v>
-      </c>
-      <c r="F66" t="n">
-        <v>80</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J66" t="n">
-        <v>1</v>
-      </c>
-      <c r="K66" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L66" t="b">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" t="n">
-        <v>-3.41938137955719</v>
-      </c>
-      <c r="O66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>29</v>
-      </c>
-      <c r="B67" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D67" t="n">
-        <v>-0.0387831522775009</v>
-      </c>
-      <c r="E67" t="n">
-        <v>-0.0560462586194153</v>
-      </c>
-      <c r="F67" t="n">
-        <v>16</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J67" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L67" t="b">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>1</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-12.9248645315104</v>
-      </c>
-      <c r="O67" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>29</v>
-      </c>
-      <c r="B68" t="s">
-        <v>25</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-0.0324383672669297</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-0.049555432229209</v>
-      </c>
-      <c r="F68" t="n">
-        <v>80</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L68" t="b">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N68" t="n">
-        <v>-5.14836231034565</v>
-      </c>
-      <c r="O68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>29</v>
-      </c>
-      <c r="B69" t="s">
-        <v>25</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D69" t="n">
-        <v>-0.0608143953956439</v>
-      </c>
-      <c r="E69" t="n">
-        <v>-0.0799724909308915</v>
-      </c>
-      <c r="F69" t="n">
-        <v>16</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J69" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L69" t="b">
-        <v>0</v>
-      </c>
-      <c r="M69" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="N69" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="O69"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70" t="s">
-        <v>26</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D70" t="n">
-        <v>-0.0192426932700829</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-0.0321081968278416</v>
-      </c>
-      <c r="F70" t="n">
-        <v>80</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J70" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L70" t="b">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N70" t="n">
-        <v>-3.41938137955719</v>
-      </c>
-      <c r="O70" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>29</v>
-      </c>
-      <c r="B71" t="s">
-        <v>26</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D71" t="n">
-        <v>-0.0353401499116603</v>
-      </c>
-      <c r="E71" t="n">
-        <v>-0.0652567331747006</v>
-      </c>
-      <c r="F71" t="n">
-        <v>16</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J71" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L71" t="b">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>1</v>
-      </c>
-      <c r="N71" t="n">
-        <v>-6.82295794977887</v>
-      </c>
-      <c r="O71" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>29</v>
-      </c>
-      <c r="B72" t="s">
-        <v>27</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D72" t="n">
-        <v>-0.0343868077922034</v>
-      </c>
-      <c r="E72" t="n">
-        <v>-0.0520885669761088</v>
-      </c>
-      <c r="F72" t="n">
-        <v>80</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1</v>
-      </c>
-      <c r="K72" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L72" t="b">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>1</v>
-      </c>
-      <c r="N72" t="n">
-        <v>-11.9357650167846</v>
-      </c>
-      <c r="O72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>29</v>
-      </c>
-      <c r="B73" t="s">
-        <v>27</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D73" t="n">
-        <v>-0.0609893262255769</v>
-      </c>
-      <c r="E73" t="n">
-        <v>-0.0796933139464944</v>
-      </c>
-      <c r="F73" t="n">
-        <v>16</v>
-      </c>
-      <c r="G73" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L73" t="b">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>1</v>
-      </c>
-      <c r="N73" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O73" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>30</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D74" t="n">
-        <v>-0.00754861233167929</v>
-      </c>
-      <c r="E74" t="n">
-        <v>-0.0105209176347553</v>
-      </c>
-      <c r="F74" t="n">
-        <v>80</v>
-      </c>
-      <c r="G74" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L74" t="b">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" t="n">
-        <v>-0.919537512706029</v>
-      </c>
-      <c r="O74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>30</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D75" t="n">
-        <v>-0.0124026305340209</v>
-      </c>
-      <c r="E75" t="n">
-        <v>-0.0148602611677199</v>
-      </c>
-      <c r="F75" t="n">
-        <v>16</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J75" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L75" t="b">
-        <v>0</v>
-      </c>
-      <c r="M75" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="N75" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="O75"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>30</v>
-      </c>
-      <c r="B76" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D76" t="n">
-        <v>-0.00911944784032187</v>
-      </c>
-      <c r="E76" t="n">
-        <v>-0.0132812972068286</v>
-      </c>
-      <c r="F76" t="n">
-        <v>80</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J76" t="n">
-        <v>1</v>
-      </c>
-      <c r="K76" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L76" t="b">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>-7.15776445500614</v>
-      </c>
-      <c r="O76" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>30</v>
-      </c>
-      <c r="B77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D77" t="n">
-        <v>-0.0155851122796263</v>
-      </c>
-      <c r="E77" t="n">
-        <v>-0.0201299838969888</v>
-      </c>
-      <c r="F77" t="n">
-        <v>16</v>
-      </c>
-      <c r="G77" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J77" t="n">
-        <v>1</v>
-      </c>
-      <c r="K77" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L77" t="b">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>1</v>
-      </c>
-      <c r="N77" t="n">
-        <v>-12.9248645315104</v>
-      </c>
-      <c r="O77" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>30</v>
-      </c>
-      <c r="B78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D78" t="n">
-        <v>-0.00860127870257976</v>
-      </c>
-      <c r="E78" t="n">
-        <v>-0.0121924863007988</v>
-      </c>
-      <c r="F78" t="n">
-        <v>80</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J78" t="n">
-        <v>1</v>
-      </c>
-      <c r="K78" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L78" t="b">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" t="n">
-        <v>-3.53315674889939</v>
-      </c>
-      <c r="O78" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>30</v>
-      </c>
-      <c r="B79" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D79" t="n">
-        <v>-0.0143248346854156</v>
-      </c>
-      <c r="E79" t="n">
-        <v>-0.0184925557173553</v>
-      </c>
-      <c r="F79" t="n">
-        <v>16</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J79" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L79" t="b">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O79" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D80" t="n">
-        <v>-0.0150146688563622</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-0.0196577871163292</v>
-      </c>
-      <c r="F80" t="n">
-        <v>80</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J80" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L80" t="b">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" t="n">
-        <v>-0.000738587034106786</v>
-      </c>
-      <c r="O80" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" t="s">
-        <v>19</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D81" t="n">
-        <v>-0.0227928020226114</v>
-      </c>
-      <c r="E81" t="n">
-        <v>-0.0266621186222709</v>
-      </c>
-      <c r="F81" t="n">
-        <v>16</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J81" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L81" t="b">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>1</v>
-      </c>
-      <c r="N81" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>30</v>
-      </c>
-      <c r="B82" t="s">
-        <v>20</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D82" t="n">
-        <v>-0.0138914068488272</v>
-      </c>
-      <c r="E82" t="n">
-        <v>-0.0178454572159039</v>
-      </c>
-      <c r="F82" t="n">
-        <v>80</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J82" t="n">
-        <v>1</v>
-      </c>
-      <c r="K82" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L82" t="b">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>1</v>
-      </c>
-      <c r="N82" t="n">
-        <v>-0.000738587034106786</v>
-      </c>
-      <c r="O82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>30</v>
-      </c>
-      <c r="B83" t="s">
-        <v>20</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D83" t="n">
-        <v>-0.0204316349296731</v>
-      </c>
-      <c r="E83" t="n">
-        <v>-0.0244059985239135</v>
-      </c>
-      <c r="F83" t="n">
-        <v>16</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J83" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L83" t="b">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1</v>
-      </c>
-      <c r="N83" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>30</v>
-      </c>
-      <c r="B84" t="s">
-        <v>21</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D84" t="n">
-        <v>-0.0128951328873264</v>
-      </c>
-      <c r="E84" t="n">
-        <v>-0.0167381375953736</v>
-      </c>
-      <c r="F84" t="n">
-        <v>80</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J84" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L84" t="b">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" t="n">
-        <v>-0.000738587034106786</v>
-      </c>
-      <c r="O84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>30</v>
-      </c>
-      <c r="B85" t="s">
-        <v>21</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D85" t="n">
-        <v>-0.0194035138833033</v>
-      </c>
-      <c r="E85" t="n">
-        <v>-0.0230499278479395</v>
-      </c>
-      <c r="F85" t="n">
-        <v>16</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J85" t="n">
-        <v>1</v>
-      </c>
-      <c r="K85" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L85" t="b">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>1</v>
-      </c>
-      <c r="N85" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>30</v>
-      </c>
-      <c r="B86" t="s">
-        <v>22</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D86" t="n">
-        <v>-0.0525814067934265</v>
-      </c>
-      <c r="E86" t="n">
-        <v>-0.0754043096912388</v>
-      </c>
-      <c r="F86" t="n">
-        <v>80</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J86" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L86" t="b">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>1</v>
-      </c>
-      <c r="N86" t="n">
-        <v>-1.04441805348648</v>
-      </c>
-      <c r="O86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>30</v>
-      </c>
-      <c r="B87" t="s">
-        <v>22</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D87" t="n">
-        <v>-0.0820739931626555</v>
-      </c>
-      <c r="E87" t="n">
-        <v>-0.115992143124377</v>
-      </c>
-      <c r="F87" t="n">
-        <v>16</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L87" t="b">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>1</v>
-      </c>
-      <c r="N87" t="n">
-        <v>-6.82295794977887</v>
-      </c>
-      <c r="O87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>30</v>
-      </c>
-      <c r="B88" t="s">
-        <v>23</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D88" t="n">
-        <v>-0.030018046052394</v>
-      </c>
-      <c r="E88" t="n">
-        <v>-0.0433314031886787</v>
-      </c>
-      <c r="F88" t="n">
-        <v>80</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J88" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L88" t="b">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>-2.09449567488804</v>
-      </c>
-      <c r="O88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>30</v>
-      </c>
-      <c r="B89" t="s">
-        <v>23</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-0.0466888314021974</v>
-      </c>
-      <c r="E89" t="n">
-        <v>-0.0681733955820991</v>
-      </c>
-      <c r="F89" t="n">
-        <v>16</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J89" t="n">
-        <v>1</v>
-      </c>
-      <c r="K89" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L89" t="b">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>1</v>
-      </c>
-      <c r="N89" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O89" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>30</v>
-      </c>
-      <c r="B90" t="s">
-        <v>24</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D90" t="n">
-        <v>-0.0182203536152379</v>
-      </c>
-      <c r="E90" t="n">
-        <v>-0.0314292485687419</v>
-      </c>
-      <c r="F90" t="n">
-        <v>80</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J90" t="n">
-        <v>1</v>
-      </c>
-      <c r="K90" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L90" t="b">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>-3.41938137955719</v>
-      </c>
-      <c r="O90" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>30</v>
-      </c>
-      <c r="B91" t="s">
-        <v>24</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D91" t="n">
-        <v>-0.0387831522775009</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-0.0560462586194153</v>
-      </c>
-      <c r="F91" t="n">
-        <v>16</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J91" t="n">
-        <v>1</v>
-      </c>
-      <c r="K91" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L91" t="b">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>-12.9248645315104</v>
-      </c>
-      <c r="O91" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>30</v>
-      </c>
-      <c r="B92" t="s">
-        <v>25</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D92" t="n">
-        <v>-0.0324383672669297</v>
-      </c>
-      <c r="E92" t="n">
-        <v>-0.049555432229209</v>
-      </c>
-      <c r="F92" t="n">
-        <v>80</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J92" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L92" t="b">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>1</v>
-      </c>
-      <c r="N92" t="n">
-        <v>-5.14836231034565</v>
-      </c>
-      <c r="O92" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>30</v>
-      </c>
-      <c r="B93" t="s">
-        <v>25</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D93" t="n">
-        <v>-0.0608143953956439</v>
-      </c>
-      <c r="E93" t="n">
-        <v>-0.0799724909308915</v>
-      </c>
-      <c r="F93" t="n">
-        <v>16</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J93" t="n">
-        <v>1</v>
-      </c>
-      <c r="K93" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L93" t="b">
-        <v>0</v>
-      </c>
-      <c r="M93" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="N93" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="O93"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>30</v>
-      </c>
-      <c r="B94" t="s">
-        <v>26</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D94" t="n">
-        <v>-0.0192426932700829</v>
-      </c>
-      <c r="E94" t="n">
-        <v>-0.0321081968278416</v>
-      </c>
-      <c r="F94" t="n">
-        <v>80</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J94" t="n">
-        <v>1</v>
-      </c>
-      <c r="K94" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L94" t="b">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>1</v>
-      </c>
-      <c r="N94" t="n">
-        <v>-3.41938137955719</v>
-      </c>
-      <c r="O94" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>30</v>
-      </c>
-      <c r="B95" t="s">
-        <v>26</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-0.0353401499116603</v>
-      </c>
-      <c r="E95" t="n">
-        <v>-0.0652567331747006</v>
-      </c>
-      <c r="F95" t="n">
-        <v>16</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L95" t="b">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-6.82295794977887</v>
-      </c>
-      <c r="O95" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>30</v>
-      </c>
-      <c r="B96" t="s">
-        <v>27</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D96" t="n">
-        <v>-0.0343868077922034</v>
-      </c>
-      <c r="E96" t="n">
-        <v>-0.0520885669761088</v>
-      </c>
-      <c r="F96" t="n">
-        <v>80</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0.0506008855154965</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J96" t="n">
-        <v>1</v>
-      </c>
-      <c r="K96" t="n">
-        <v>-0.0119723751888046</v>
-      </c>
-      <c r="L96" t="b">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1</v>
-      </c>
-      <c r="N96" t="n">
-        <v>-11.9357650167846</v>
-      </c>
-      <c r="O96" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>30</v>
-      </c>
-      <c r="B97" t="s">
-        <v>27</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D97" t="n">
-        <v>-0.0609893262255769</v>
-      </c>
-      <c r="E97" t="n">
-        <v>-0.0796933139464944</v>
-      </c>
-      <c r="F97" t="n">
-        <v>16</v>
-      </c>
-      <c r="G97" t="n">
-        <v>1581</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0.0101201771030993</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J97" t="n">
-        <v>1</v>
-      </c>
-      <c r="K97" t="n">
-        <v>-0.00229733781463892</v>
-      </c>
-      <c r="L97" t="b">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>1</v>
-      </c>
-      <c r="N97" t="n">
-        <v>-2.05479571547011</v>
-      </c>
-      <c r="O97" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5014,27 +2748,27 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>0.95</v>
@@ -5060,7 +2794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>0.99</v>
@@ -5086,7 +2820,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>0.95</v>
@@ -5112,7 +2846,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>0.99</v>
@@ -5138,7 +2872,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B6" t="n">
         <v>0.95</v>
@@ -5164,7 +2898,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B7" t="n">
         <v>0.99</v>
